--- a/public/sites.xlsx
+++ b/public/sites.xlsx
@@ -413,10 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="150" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
@@ -427,15 +426,11 @@
     <col width="320" customWidth="1" min="9" max="9"/>
     <col width="320" customWidth="1" min="10" max="10"/>
     <col width="320" customWidth="1" min="11" max="11"/>
-    <col width="320" customWidth="1" min="12" max="12"/>
-    <col width="320" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
-    <col width="320" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="110" customWidth="1" min="17" max="17"/>
-    <col width="150" customWidth="1" min="18" max="18"/>
-    <col width="150" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+    <col width="110" customWidth="1" min="13" max="13"/>
+    <col width="150" customWidth="1" min="14" max="14"/>
+    <col width="150" customWidth="1" min="15" max="15"/>
+    <col width="150" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,50 +486,30 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>其他2·白嫖org</t>
+          <t>模型</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>其他3·飞书合集</t>
+          <t>响应</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>其他4·幻城导航</t>
+          <t>渠道状态</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>验证</t>
+          <t>注册链接</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>模型</t>
+          <t>签到地址</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>响应</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>渠道状态</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>注册链接</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>签到地址</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
         <is>
           <t>uid</t>
         </is>
@@ -576,35 +551,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>下载agent软件，但是对小白友好</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>白嫖org:基元律动的好友邀请活动已延长；好友完成注册并下载使用 opensquilla 后，可获得价值 68 元的 token 额度，同时还能用统一 api key 接入多模型。 | 标签:免费api,opensquilla,邀请活动,openai兼容,claude兼容</t>
-        </is>
-      </c>
+          <t>一个北京的企业的网站，下载agent软件，但是对小白友好</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>幻城导航:一个北京的企业的网站，注册送六十多块钱的token，正常价格调用，邀请人又是六十多，嘎嘎爽，速来 | 社区评分5.0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://tokenrhythm.studio/i/rf_tr_Nii7WjYsktO0e-CAC4HMhEpC</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>https://tokenrhythm.studio/i/rf_tr_Nii7WjYsktO0e-CAC4HMhEpC</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://tokenrhythm.studio/account/referrals</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>fa3fe23d</t>
         </is>
@@ -646,23 +605,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>下载agent软件，但是对小白友好</t>
+          <t>智谱的agent，下载agent软件，但是对小白友好</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://zcode.z.ai</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>https://zcode.z.ai</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>330328b3</t>
         </is>
@@ -677,7 +632,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>失效</t>
+          <t>有效</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -714,34 +669,22 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>白嫖org:agentrouter 是一条速度很快的公益 api 线路，目前可用 claude opus 4.8 和 gpt-5.6 sol。首次注册可领 175 美元新人额度，通过本页 aff 邀请入口注册还可拿到 50 美元邀请额度。 | 标签:免费api,claude,gpt,claude code,opus 4.8,gpt-5.6 sol,注册送额度</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+          <t>claude,gpt,claude code,opus 4.8,gpt-5.6 sol</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8.29</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
           <t>https://agentrouter.org/register?aff=CzEG</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>https://agentrouter.org/console</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>重登</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>0c9d56c3</t>
         </is>
@@ -786,36 +729,20 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>白嫖org:nofx 注册送 20 积分，每日签到送 5 积分，每成功邀请一位好友再得 5 积分；积分可用于主流模型，优势是分组倍率较低，适合先用免费额度做日常体验。 | 标签:免费api,注册送积分,每日签到,邀请奖励,低倍率,主流模型</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8.29</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
           <t>https://nofx.one/zh-CN/sign-in?ref=91CFCXG7</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://nofx.one/zh-CN/tasks</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Discord签到</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>c5834223</t>
         </is>
@@ -849,23 +776,11 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>https://api.sharezzz.com/register?aff=HGU6HK4RHW6A</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>https://api.sharezzz.com/register?aff=HGU6HK4RHW6A</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>https://api.sharezzz.com/dashboard</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>c5de4347</t>
         </is>
@@ -901,33 +816,25 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>白嫖org:gemini 和 grok 免费、claude 走收费的公益站，受邀注册送 10 刀、每天签到再补 2–5 刀，综合倍率 0.5。站子风格比较「猛男」、口味重，介意的绕道；冲着免费 gemini / grok 来的可以薅。openai 兼容直连。 | 标签:免费api,gemini,grok,限免,每日签到</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>飞书合集档位:NPC(能签尽量签,蚊子再小也是肉)</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>冲着免费 gemini / grok 来的可以薅。openai 兼容直连</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://api.rua.chat/sign-up?aff=Lxge</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://api.rua.chat/dashboard/overview</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>143d3a0d</t>
         </is>
@@ -977,31 +884,15 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>幻城导航:有人投稿说本站是垃圾，故已批准同意，欢迎大家访问垃圾 | 社区评分5.0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://api.hcnsec.cn/</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>https://api.hcnsec.cn/</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://api.hcnsec.cn/profile</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>c263d9ef</t>
         </is>
@@ -1014,7 +905,11 @@
           <t>维云</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NPC</t>
@@ -1027,7 +922,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>每天奖励，第五天白嫖保底能用sol</t>
+          <t>每2小时1次抽卡</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1037,7 +932,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>模型全但是有点降智</t>
+          <t>模型全但是有点降智；著名注水公益站</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1050,32 +945,20 @@
           <t>耐蹬；还能抽卡，额度用不完，任务跑得太慢像在演我</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>白嫖org:免费区直接挂着 claude-opus-4-8-free、glm-5.2-free 还有一票国产开源的公益大站，每天领一份保底套餐、还能多次抽奖攒小额额度。模型杂、站子稳，openai 兼容，拿来当长期备用很顶。 | 标签:免费api,claude,开源模型,限免,每日签到,生图</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>飞书合集档位:拉完了(额度少事儿多,极不推荐,但倍率小适合当付费站)</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://vsllm.com/i/KqXK</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>https://vsllm.com/console/personal</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>fa8703ed</t>
         </is>
@@ -1097,7 +980,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1000每日过期</t>
+          <t>1000-2000每日过期</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1105,43 +988,31 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>著名注水公益站</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>解锁邀请任务才能依次解锁模型，有点折磨人了</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>白嫖org:新人注册立得 5000 点免费额度，每日签到再领 1000~3000 点，免费用 claude opus 4.5 / sonnet 4.5、gemini 3.1 pro 等大模型，按「额度/次」扣的公益免费线路。 | 标签:免费api,claude,gemini,deepseek,每日签到</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>飞书合集档位:NPC(能签尽量签,蚊子再小也是肉)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>幻城导航:这家注册送的挺多，每天刷新，邀请人送的也特别多，但是模型疑似都是假的，有内置提示词注入，然后模型能力看起来很垃圾，不过好在可以白嫖的额度很多，你要是不挑模型，这个就随便，反正能白嫖的量大，付钱还是算了</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://free.supxh.xin/register?code=XR4HB7</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://free.supxh.xin/dashboard</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>79acd704</t>
         </is>
@@ -1156,7 +1027,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>复活了</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1180,26 +1051,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>白嫖org:模型多到挑花眼的公益免费 api 站，自家「银狮」币制、10 银狮兑 1 刀。注册到手 200 银狮，签到还随机爆送（我一发签到就进账 1324 银狮）。一把 key 拉出来一百多个模型——grok 4 全家桶、deepseek-v4、qwen3.5、glm5.1、kimi、minimax、小米 mimo、llama4 全在，openai 兼容直接接客户端。 | 标签:免费api,deepseek,grok,qwen,kimi,注册送额度</t>
+          <t>claude-opus-4-8、claude-opus-4-8-thinking、claude-opus-5、claude-opus-5-thinking 四款 claude opus 模型</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://new.xinjianya.top/register?aff=ocjL</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>https://new.xinjianya.top/console/personal</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>55214b55</t>
         </is>
@@ -1232,28 +1099,20 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>白嫖org:kktoken 注册送 100 额度、每日签到送 20，目前提供 claude-opus-4-8、claude-opus-4-8-thinking、claude-opus-5、claude-opus-5-thinking 四款 claude opus 模型。 | 标签:免费api,claude,claude opus,claude code,注册送额度,每日签到</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://kktoken.cc/sign-up?aff=2drd</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>https://kktoken.cc/profile</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>114a3af8</t>
         </is>
@@ -1268,7 +1127,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1294,32 +1153,16 @@
           <t>调用经常错误，不稳定，PRM时高时低</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>白嫖org:gorouter 是一套 new api 风格的模型控制台：当前可用 github 登录，注册开关与签到功能都处于开启状态，控制台提供令牌、用量记录、模型和兑换入口。公开状态没有列出固定赠送额度或可用模型，先登录核对再接客户端。 | 标签:公益api,github登录,每日签到,apikey,newapi</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://gorouter.app/sign-up?aff=ZIS8</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>https://gorouter.app/sign-up?aff=ZIS8</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>https://gorouter.app/profile</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>6acb8657</t>
         </is>
@@ -1356,32 +1199,16 @@
           <t>用github直接每天免费用，不用签到</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>白嫖org:chatanywhere公益站脱胎自 github 上 38.7k star 的老牌仓库 gpt_api_free——不用在站上注册账号密码，拿自己的 github 账号做一次 oauth 授权，就能领到一份长期有效的免费 key，跑 gpt、claude、deepseek、gemini 等一众主流模型。免费档按模型分了次数，够日常写代码、跑脚本用。 | 标签:免费api,github oauth,gpt,claude,deepseek,免注册</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用) [夯] anyrouter最近用不了</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://chatanywhere.tech/console/overview</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>https://chatanywhere.tech/console/overview</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>https://chatanywhere.tech/console/overview</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>8b261503</t>
         </is>
@@ -1396,7 +1223,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1414,32 +1241,16 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>白嫖org:justwoker 是一个签到送额度的公益 api，每日签到可随机获得额度。注册需要 github 账号且账号年限满一年。 | 标签:免费api,签到送额度,github 验证</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://api.justwoker.icu/register?aff=troQ</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>https://api.justwoker.icu/register?aff=troQ</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>https://api.justwoker.icu/dashboard/overview</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>998d5e4b</t>
         </is>
@@ -1481,27 +1292,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://lzhiyu.ccwu.cc/register?ref=REF-FD7D72CFB8</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://lzhiyu.ccwu.cc/dashboard</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>71836a0c</t>
         </is>
@@ -1543,27 +1346,15 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>http://781391.cc.cd/register?ref=REF-D058C0F05B</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>http://781391.cc.cd/register?ref=REF-D058C0F05B</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>http://781391.cc.cd/dashboard</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>d99ba992</t>
         </is>
@@ -1597,31 +1388,27 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>目前站点在内测阶段</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用) [夯] 辉哥（3）是最近开的新站，模型还没那么多，目前站点在内测阶段</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://7891vip.cc.cd/login?view=reg&amp;aff=evgQ</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://7891vip.cc.cd/console</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>332853e9</t>
         </is>
@@ -1631,10 +1418,14 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MiaoMu</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>XiaoMu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -1664,32 +1455,20 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>幻城导航:注册两美元，签到两美元，邀请人两美元，但是价格还算便宜，几美元就能跑几百万token，十几个美元几千万token | 社区评分5.0</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8.29</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
           <t>https://xiaomuai.cn/register?aff=9BN0</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://xiaomuai.cn/dashboard</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>fc02be97</t>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>c4e7bce6</t>
         </is>
       </c>
     </row>
@@ -1730,26 +1509,18 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>白嫖org:把 claude max、chatgpt pro、codex、gemini 这些会员号拼成号池对外开的公益站，一个网关同时吃 openai / anthropic / gemini 三种协议，还留了个免费的 gpt-5.5 pro 池。签到送积分，自己建 key 选对号池就能薅满血 opus-4-8 和 gpt-5.5。 | 标签:免费api,claude,gemini,codex,号池,每日签到</t>
+          <t>claude max、chatgpt pro、codex、gemini</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://bmapi.020212.xyz/register?aff=SZ52TQ9UP8QY</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>https://bmapi.020212.xyz/register?aff=SZ52TQ9UP8QY</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>https://bmapi.020212.xyz/keys</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>27e4c369</t>
         </is>
@@ -1787,7 +1558,11 @@
           <t>20橘子</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>有免费模型，按次模型不耐蹬，要注意</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>快，体验不错</t>
@@ -1795,27 +1570,23 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>太不耐蹬了，多攒攒；网站卡卡的</t>
+          <t>网站有时卡卡的</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://beizhi.sylu.cc/sign-up?aff=hgzY</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>https://beizhi.sylu.cc/profile</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>4765baf4</t>
         </is>
@@ -1830,7 +1601,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1860,32 +1631,16 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>白嫖org:chuan公益api 提供签到和邀请额度，签到最高送 50、邀请送 50；站点会在模型报错时尝试切换兜底模型，gemini 系列严禁用于编程或大型任务。 | 标签:免费api,签到额度,邀请奖励,openai兼容,gemini限制</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>飞书合集档位:NPC(能签尽量签,蚊子再小也是肉)</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://chuan.sylu.cc/sign-up?aff=EZfA</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>https://chuan.sylu.cc/sign-up?aff=EZfA</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>https://chuan.sylu.cc/profile</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>698c382f</t>
         </is>
@@ -1900,7 +1655,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>无效</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1928,30 +1683,18 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>白嫖org:tabitoken 是一条专攻 claude opus 全家桶的公益 api 线路，claude-opus-4-8、claude-opus-4-8-thinking、claude-opus-5、claude-opus-5-thinking 四款一次挂齐。正常注册送 $100 新人额度，通过本页 aff 邀请入口注册还能额外拿 $20 邀请额度。 | 标签:免费api,claude,claude opus,claude code,注册送额度,邀请送额度</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
+          <t>claude-opus-4-8、claude-opus-4-8-thinking、claude-opus-5、claude-opus-5-thinking</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://tabitoken.com/sign-up?aff=NvjM</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>https://tabitoken.com/sign-up?aff=NvjM</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>https://tabitoken.com/dashboard/overview</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>12d67bb1</t>
         </is>
@@ -1996,32 +1739,20 @@
           <t>耐蹬</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>白嫖org:不堆国产凑数、专挂一线旗舰的公益免费 api 站，claude opus 4.8、gemini 3.1 pro、gpt-5.5、grok 4.3 全在，模型多到要自己拉列表。注册送 100 元、每天签到再随机加，openai 兼容直连。就是免费余额够不着最贵那几个，得挑便宜款薅。 | 标签:免费api,claude,gemini,gpt,grok,注册送额度,每日签到</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>飞书合集档位:NPC(能签尽量签,蚊子再小也是肉)</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://api.gemai.cc/sign-up?aff=8UV9MlGM</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://api.gemai.cc/profile</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>f55df23c</t>
         </is>
@@ -2049,11 +1780,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0.5刀以内</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>不充值无返利</t>
@@ -2066,28 +1793,16 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>白嫖org:模型杂、可生图、跑了挺久没掉链子的公益免费大站。每天签到攒点小额额度，综合倍率 0.2–0.8 偏低，拿来当长期挂着的通用备用正合适。openai 兼容直连。 | 标签:免费api,聚合,生图,每日签到,低倍率</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://aiyiwei.vip/register?aff=nFd2</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>https://aiyiwei.vip/register?aff=nFd2</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>https://aiyiwei.vip/console</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>82238b59</t>
         </is>
@@ -2131,21 +1846,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://us-3.nianhuaapi.com/sign-up?aff=mqso</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>https://us-3.nianhuaapi.com/profile</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>3d5bd26d</t>
         </is>
@@ -2160,7 +1871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>无效</t>
+          <t>有效</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2178,32 +1889,20 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>白嫖org:注册连邮箱都不用、上来送 200 美元还能每天签到再领 60 的公益免费 api 站，挂的全是 gpt-5 / codex 一整挂编程模型，openai 兼容直连，拿去喂 codex cli、cursor 这类编程工具正合适。 | 标签:免费api,gpt-5,codex,编程白嫖,注册送额度,每日签到</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>幻城导航:注册就送两百刀，然后邀请人送60刀，只支持gpt，模型测试目前看很真实，然后价格也很正，邀请一个人用五个亿token没问题，新网站速速白嫖</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://helpcoder.cc/register?aff=3y6d</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://helpcoder.cc/console/personal</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>3957b1aa</t>
         </is>
@@ -2247,21 +1946,13 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://free.lyclaude.site/register?aff=yjxO</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>https://free.lyclaude.site/register?aff=yjxO</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>https://free.lyclaude.site/console/personal</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>2048ea37</t>
         </is>
@@ -2307,35 +1998,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>太不耐蹬了，还不能签到；是注册公司</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>白嫖org:熊猫api 按本次活动口径为新人注册赠送 200 额度、邀请用户赠送 🍚100；公开模型表覆盖 claude、gemini、deepseek、gpt 等大量模型，并兼容 openai 与 anthropic 接口。 | 标签:免费api,注册送额度,邀请奖励,claude code,gemini,deepseek,gpt</t>
-        </is>
-      </c>
+          <t>太不耐蹬了，还不能签到；是注册公司；很多模型貌似有映射，而且价格是按一千token计费，不是一百万token计费</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>幻城导航:新用户送两百刀，邀请人又是一百刀，但是这个东西的很多模型貌似有映射，而且价格是按一千token计费，不是一百万token计费，不过送的邀请额度还挺多，试试吧</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://api520.pro/register?aff=vXoD</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>https://api520.pro/register?aff=vXoD</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>https://api520.pro/console</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>35f4b395</t>
         </is>
@@ -2363,7 +2038,11 @@
           <t>5刀</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>用完每天的5刀可以写个申请20刀让AI判定</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>不充值无返利</t>
@@ -2385,27 +2064,15 @@
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用) [夯] Baaaai官方说每天免费送5-10美元，需要申请，目前我还在测试中，胆大的可以去试试</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://www.baaaai.com/register?aff=25RQ8K3XYREH</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>https://www.baaaai.com/register?aff=25RQ8K3XYREH</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>https://www.baaaai.com/keys</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>46310e45</t>
         </is>
@@ -2455,31 +2122,19 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>飞书合集档位:夯(推荐每天签到,给的额度多,额度耐用)</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>幻城导航:通过链接注册送50刀，claude grok4.6 国模都有 半公益，每日签到5-50刀，需要discord或者谷歌账号验证</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://vyceai.com/signup?ref=VYCE_G8KE59</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>https://vyceai.com/dashboard-v2</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>96706d26</t>
         </is>
@@ -2519,17 +2174,13 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://ai.txcxgzs.com/sign-up?aff=bFwh</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>https://ai.txcxgzs.com/sign-up?aff=bFwh</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>2295d037</t>
         </is>
@@ -2578,34 +2229,190 @@
           <t>瞪得太快了</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>白嫖org:不堆国产凑数、专挂一线旗舰的公益免费 api 站，claude opus 4.8、gemini 3.1 pro、gpt-5.5、grok 4.3 全在，模型多到要自己拉列表。注册送 100 元、每天签到再随机加，openai 兼容直连。就是免费余额够不着最贵那几个，得挑便宜款薅。 | 标签:免费api,claude,gemini,gpt,grok,注册送额度,每日签到</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>飞书合集档位:NPC(能签尽量签,蚊子再小也是肉)</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://api.gemai.cc/sign-up?aff=8UV9MlGM</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://api.gemai.cc/profile</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>44a25fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>DoCode</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>300刀</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://docode.cc/register?aff=ecy3</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>11d75fae</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cheap</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20刀</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>20刀</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2倍codex</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://api.cheapcodex.online/register?aff=5MJU36TMTDQL</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>https://api.cheapcodex.online/affiliate/program</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>7d3162c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>呜哩</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>有效</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>免费生图站</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://wuli.art/generate</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>c2323a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Grox</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>有个100刀日卡兑换码，需要加qq群绑定</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://www.mcgrox.top/register?aff=4CMDR24JDPM4</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>04252d90</t>
         </is>
       </c>
     </row>
